--- a/ADD-ARTEFACT-XDM/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T13:57:35+00:00</t>
+    <t>2026-07-07T20:41:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ADD-ARTEFACT-XDM/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T20:41:51+00:00</t>
+    <t>2026-07-09T18:09:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
